--- a/tams-invest-parent/tams-invest-trade/src/main/resources/tpl/TrdBondToStock001.xlsx
+++ b/tams-invest-parent/tams-invest-trade/src/main/resources/tpl/TrdBondToStock001.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="22130"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\code\BS-1.9devbranches2.1.1\tams-invest-parent\tams-invest-trade\src\main\resources\tpl\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\code\ChongQingTouZi\tams\tams-invest-parent\tams-invest-trade\src\main\resources\tpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{229A4E45-1DBB-4888-83E8-C7425F555C6F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
     <t>业务编号</t>
   </si>
@@ -54,9 +53,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>转股券面总额</t>
-  </si>
-  <si>
     <t>转股价</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -94,13 +90,20 @@
   </si>
   <si>
     <t>备注</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>转股券面总额/万元</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <numFmts count="1">
+    <numFmt numFmtId="176" formatCode="0.0000_ "/>
+  </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -174,11 +177,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="176" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -197,7 +203,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -272,23 +278,6 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri" panose="020F0502020204030204"/>
@@ -324,23 +313,6 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -516,11 +488,13 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:T2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="17" width="15.625" customWidth="1"/>
+    <col min="1" max="8" width="15.625" customWidth="1"/>
+    <col min="9" max="9" width="15.625" style="6" customWidth="1"/>
+    <col min="10" max="17" width="15.625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:20" s="1" customFormat="1" x14ac:dyDescent="0.15">
@@ -548,44 +522,46 @@
       <c r="H1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="O1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="P1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="Q1" s="2" t="s">
         <v>16</v>
-      </c>
-      <c r="Q1" s="2" t="s">
-        <v>17</v>
       </c>
       <c r="R1" s="2" t="s">
         <v>3</v>
       </c>
       <c r="S1" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="T1" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="2" t="s">
-        <v>19</v>
-      </c>
     </row>
-    <row r="2" spans="1:20" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="2" spans="1:20" s="3" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="I2" s="5"/>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
